--- a/inventories/baseline/lci-Lakkor-Tso.xlsx
+++ b/inventories/baseline/lci-Lakkor-Tso.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://leidenuniv1-my.sharepoint.com/personal/istrateir_vuw_leidenuniv_nl/Documents/Research/lithium-brine-prospective-LCA/inventories/raw/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_9F6987E5B6F80FD3AC7448EE2D7C666767025463" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5865" yWindow="1365" windowWidth="28800" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Lakkor Tso" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -229,8 +223,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -276,21 +270,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -328,7 +314,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -362,7 +348,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -397,10 +382,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -573,11 +557,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F259"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -585,7 +569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -593,7 +577,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -601,7 +585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -609,7 +593,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -617,7 +601,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -625,7 +609,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -633,7 +617,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -641,12 +625,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6">
       <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -666,12 +650,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
         <v>15</v>
       </c>
       <c r="B12">
-        <v>2.5000000000000001E-4</v>
+        <v>0.00025</v>
       </c>
       <c r="D12" t="s">
         <v>16</v>
@@ -683,12 +667,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
         <v>19</v>
       </c>
       <c r="B13">
-        <v>1.25E-3</v>
+        <v>0.00125</v>
       </c>
       <c r="D13" t="s">
         <v>16</v>
@@ -700,7 +684,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -717,12 +701,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
         <v>22</v>
       </c>
       <c r="B15">
-        <v>7.2059999999999997E-3</v>
+        <v>0.007206</v>
       </c>
       <c r="C15" t="s">
         <v>23</v>
@@ -734,7 +718,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6">
       <c r="A17" s="1" t="s">
         <v>2</v>
       </c>
@@ -742,7 +726,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -750,7 +734,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -758,7 +742,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6">
       <c r="A20" t="s">
         <v>6</v>
       </c>
@@ -766,7 +750,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6">
       <c r="A21" t="s">
         <v>7</v>
       </c>
@@ -774,7 +758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -782,7 +766,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6">
       <c r="A23" t="s">
         <v>10</v>
       </c>
@@ -790,12 +774,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6">
       <c r="A24" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6">
       <c r="A25" t="s">
         <v>13</v>
       </c>
@@ -815,7 +799,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6">
       <c r="A26" t="s">
         <v>27</v>
       </c>
@@ -832,7 +816,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6">
       <c r="A27" t="s">
         <v>30</v>
       </c>
@@ -849,7 +833,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6">
       <c r="A28" t="s">
         <v>32</v>
       </c>
@@ -866,12 +850,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6">
       <c r="A29" t="s">
         <v>15</v>
       </c>
       <c r="B29">
-        <v>1.1111111111111099E-4</v>
+        <v>0.000111111111111111</v>
       </c>
       <c r="D29" t="s">
         <v>16</v>
@@ -883,7 +867,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6">
       <c r="A30" t="s">
         <v>26</v>
       </c>
@@ -900,7 +884,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6">
       <c r="A31" t="s">
         <v>3</v>
       </c>
@@ -917,12 +901,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6">
       <c r="A32" t="s">
         <v>33</v>
       </c>
       <c r="B32">
-        <v>1.1111111111111109</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="C32" t="s">
         <v>1</v>
@@ -934,12 +918,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6">
       <c r="A33" t="s">
         <v>34</v>
       </c>
       <c r="B33">
-        <v>-1.111111111111111E-4</v>
+        <v>-0.0001111111111111111</v>
       </c>
       <c r="C33" t="s">
         <v>1</v>
@@ -951,7 +935,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6">
       <c r="A35" s="1" t="s">
         <v>2</v>
       </c>
@@ -959,7 +943,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6">
       <c r="A36" t="s">
         <v>4</v>
       </c>
@@ -967,7 +951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6">
       <c r="A37" t="s">
         <v>5</v>
       </c>
@@ -975,7 +959,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6">
       <c r="A38" t="s">
         <v>6</v>
       </c>
@@ -983,7 +967,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6">
       <c r="A39" t="s">
         <v>7</v>
       </c>
@@ -991,7 +975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6">
       <c r="A40" t="s">
         <v>8</v>
       </c>
@@ -999,7 +983,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6">
       <c r="A41" t="s">
         <v>10</v>
       </c>
@@ -1007,12 +991,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6">
       <c r="A42" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6">
       <c r="A43" t="s">
         <v>13</v>
       </c>
@@ -1032,7 +1016,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6">
       <c r="A44" t="s">
         <v>35</v>
       </c>
@@ -1049,7 +1033,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6">
       <c r="A45" t="s">
         <v>3</v>
       </c>
@@ -1066,12 +1050,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6">
       <c r="A46" t="s">
         <v>36</v>
       </c>
       <c r="B46">
-        <v>1.8768328445747811</v>
+        <v>1.876832844574781</v>
       </c>
       <c r="C46" t="s">
         <v>1</v>
@@ -1083,12 +1067,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6">
       <c r="A47" t="s">
         <v>37</v>
       </c>
       <c r="B47">
-        <v>0.58696660245601218</v>
+        <v>0.5869666024560122</v>
       </c>
       <c r="C47" t="s">
         <v>1</v>
@@ -1100,12 +1084,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6">
       <c r="A48" t="s">
         <v>39</v>
       </c>
       <c r="B48">
-        <v>6.333333333333333E-4</v>
+        <v>0.0006333333333333333</v>
       </c>
       <c r="C48" t="s">
         <v>40</v>
@@ -1117,12 +1101,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6">
       <c r="A49" t="s">
         <v>22</v>
       </c>
       <c r="B49">
-        <v>2.1252239870674489E-3</v>
+        <v>0.002125223987067449</v>
       </c>
       <c r="C49" t="s">
         <v>23</v>
@@ -1134,12 +1118,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6">
       <c r="A50" t="s">
         <v>41</v>
       </c>
       <c r="B50">
-        <v>-2.9999999999999997E-4</v>
+        <v>-0.0003</v>
       </c>
       <c r="C50" t="s">
         <v>40</v>
@@ -1151,7 +1135,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6">
       <c r="A52" s="1" t="s">
         <v>2</v>
       </c>
@@ -1159,7 +1143,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6">
       <c r="A53" t="s">
         <v>4</v>
       </c>
@@ -1167,7 +1151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6">
       <c r="A54" t="s">
         <v>5</v>
       </c>
@@ -1175,7 +1159,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6">
       <c r="A55" t="s">
         <v>6</v>
       </c>
@@ -1183,7 +1167,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6">
       <c r="A56" t="s">
         <v>7</v>
       </c>
@@ -1191,7 +1175,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6">
       <c r="A57" t="s">
         <v>8</v>
       </c>
@@ -1199,7 +1183,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6">
       <c r="A58" t="s">
         <v>10</v>
       </c>
@@ -1207,12 +1191,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6">
       <c r="A59" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6">
       <c r="A60" t="s">
         <v>13</v>
       </c>
@@ -1232,12 +1216,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6">
       <c r="A61" t="s">
         <v>43</v>
       </c>
       <c r="B61">
-        <v>-0.12674481520247191</v>
+        <v>-0.1267448152024719</v>
       </c>
       <c r="D61" t="s">
         <v>38</v>
@@ -1249,7 +1233,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6">
       <c r="A62" t="s">
         <v>42</v>
       </c>
@@ -1266,7 +1250,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6">
       <c r="A63" t="s">
         <v>44</v>
       </c>
@@ -1283,12 +1267,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6">
       <c r="A64" t="s">
         <v>37</v>
       </c>
       <c r="B64">
-        <v>0.98631102182179886</v>
+        <v>0.9863110218217989</v>
       </c>
       <c r="C64" t="s">
         <v>1</v>
@@ -1300,7 +1284,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6">
       <c r="A66" s="1" t="s">
         <v>2</v>
       </c>
@@ -1308,7 +1292,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6">
       <c r="A67" t="s">
         <v>4</v>
       </c>
@@ -1316,7 +1300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6">
       <c r="A68" t="s">
         <v>5</v>
       </c>
@@ -1324,7 +1308,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6">
       <c r="A69" t="s">
         <v>6</v>
       </c>
@@ -1332,7 +1316,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6">
       <c r="A70" t="s">
         <v>7</v>
       </c>
@@ -1340,7 +1324,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6">
       <c r="A71" t="s">
         <v>8</v>
       </c>
@@ -1348,7 +1332,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6">
       <c r="A72" t="s">
         <v>10</v>
       </c>
@@ -1356,12 +1340,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="73" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6">
       <c r="A73" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6">
       <c r="A74" t="s">
         <v>13</v>
       </c>
@@ -1381,7 +1365,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6">
       <c r="A75" t="s">
         <v>45</v>
       </c>
@@ -1398,12 +1382,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6">
       <c r="A76" t="s">
         <v>3</v>
       </c>
       <c r="B76">
-        <v>0.27692963221269312</v>
+        <v>0.2769296322126931</v>
       </c>
       <c r="C76" t="s">
         <v>1</v>
@@ -1415,12 +1399,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6">
       <c r="A77" t="s">
         <v>26</v>
       </c>
       <c r="B77">
-        <v>0.65383795973413361</v>
+        <v>0.6538379597341336</v>
       </c>
       <c r="C77" t="s">
         <v>1</v>
@@ -1432,7 +1416,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6">
       <c r="A78" t="s">
         <v>37</v>
       </c>
@@ -1449,12 +1433,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6">
       <c r="A79" t="s">
         <v>46</v>
       </c>
       <c r="B79">
-        <v>6.9232408053173281E-2</v>
+        <v>0.06923240805317328</v>
       </c>
       <c r="C79" t="s">
         <v>47</v>
@@ -1466,7 +1450,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="81" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6">
       <c r="A81" s="1" t="s">
         <v>2</v>
       </c>
@@ -1474,7 +1458,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6">
       <c r="A82" t="s">
         <v>4</v>
       </c>
@@ -1482,7 +1466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6">
       <c r="A83" t="s">
         <v>5</v>
       </c>
@@ -1490,7 +1474,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6">
       <c r="A84" t="s">
         <v>6</v>
       </c>
@@ -1498,7 +1482,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6">
       <c r="A85" t="s">
         <v>7</v>
       </c>
@@ -1506,7 +1490,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6">
       <c r="A86" t="s">
         <v>8</v>
       </c>
@@ -1514,7 +1498,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6">
       <c r="A87" t="s">
         <v>10</v>
       </c>
@@ -1522,12 +1506,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="88" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6">
       <c r="A88" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6">
       <c r="A89" t="s">
         <v>13</v>
       </c>
@@ -1547,7 +1531,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6">
       <c r="A90" t="s">
         <v>48</v>
       </c>
@@ -1564,12 +1548,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6">
       <c r="A91" t="s">
         <v>42</v>
       </c>
       <c r="B91">
-        <v>7.7164002898357591</v>
+        <v>7.716400289835759</v>
       </c>
       <c r="C91" t="s">
         <v>1</v>
@@ -1581,12 +1565,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6">
       <c r="A92" t="s">
         <v>22</v>
       </c>
       <c r="B92">
-        <v>8.9565360507022195E-3</v>
+        <v>0.00895653605070222</v>
       </c>
       <c r="C92" t="s">
         <v>23</v>
@@ -1598,12 +1582,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6">
       <c r="A93" t="s">
         <v>34</v>
       </c>
       <c r="B93">
-        <v>-6.7164002898357587E-3</v>
+        <v>-0.006716400289835759</v>
       </c>
       <c r="C93" t="s">
         <v>1</v>
@@ -1615,7 +1599,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6">
       <c r="A95" s="1" t="s">
         <v>2</v>
       </c>
@@ -1623,7 +1607,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6">
       <c r="A96" t="s">
         <v>4</v>
       </c>
@@ -1631,7 +1615,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6">
       <c r="A97" t="s">
         <v>5</v>
       </c>
@@ -1639,7 +1623,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6">
       <c r="A98" t="s">
         <v>6</v>
       </c>
@@ -1647,7 +1631,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6">
       <c r="A99" t="s">
         <v>7</v>
       </c>
@@ -1655,7 +1639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6">
       <c r="A100" t="s">
         <v>8</v>
       </c>
@@ -1663,7 +1647,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6">
       <c r="A101" t="s">
         <v>10</v>
       </c>
@@ -1671,12 +1655,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="102" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6">
       <c r="A102" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6">
       <c r="A103" t="s">
         <v>13</v>
       </c>
@@ -1696,7 +1680,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6">
       <c r="A104" t="s">
         <v>49</v>
       </c>
@@ -1713,12 +1697,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6">
       <c r="A105" t="s">
         <v>45</v>
       </c>
       <c r="B105">
-        <v>17.956655117655551</v>
+        <v>17.95665511765555</v>
       </c>
       <c r="C105" t="s">
         <v>1</v>
@@ -1730,12 +1714,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6">
       <c r="A106" t="s">
         <v>22</v>
       </c>
       <c r="B106">
-        <v>2.0842546118707339E-2</v>
+        <v>0.02084254611870734</v>
       </c>
       <c r="C106" t="s">
         <v>23</v>
@@ -1747,12 +1731,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6">
       <c r="A107" t="s">
         <v>34</v>
       </c>
       <c r="B107">
-        <v>3.9113854001251057E-3</v>
+        <v>0.003911385400125106</v>
       </c>
       <c r="C107" t="s">
         <v>1</v>
@@ -1764,7 +1748,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="109" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6">
       <c r="A109" s="1" t="s">
         <v>2</v>
       </c>
@@ -1772,7 +1756,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6">
       <c r="A110" t="s">
         <v>4</v>
       </c>
@@ -1780,7 +1764,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6">
       <c r="A111" t="s">
         <v>5</v>
       </c>
@@ -1788,7 +1772,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6">
       <c r="A112" t="s">
         <v>6</v>
       </c>
@@ -1796,7 +1780,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6">
       <c r="A113" t="s">
         <v>7</v>
       </c>
@@ -1804,7 +1788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6">
       <c r="A114" t="s">
         <v>8</v>
       </c>
@@ -1812,7 +1796,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6">
       <c r="A115" t="s">
         <v>10</v>
       </c>
@@ -1820,12 +1804,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6">
       <c r="A116" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6">
       <c r="A117" t="s">
         <v>13</v>
       </c>
@@ -1845,7 +1829,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6">
       <c r="A118" t="s">
         <v>50</v>
       </c>
@@ -1862,7 +1846,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6">
       <c r="A119" t="s">
         <v>51</v>
       </c>
@@ -1879,12 +1863,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6">
       <c r="A120" t="s">
         <v>22</v>
       </c>
       <c r="B120">
-        <v>2.708333333333333E-3</v>
+        <v>0.002708333333333333</v>
       </c>
       <c r="C120" t="s">
         <v>23</v>
@@ -1896,12 +1880,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6">
       <c r="A121" t="s">
         <v>34</v>
       </c>
       <c r="B121">
-        <v>-1.3333333333333331E-3</v>
+        <v>-0.001333333333333333</v>
       </c>
       <c r="C121" t="s">
         <v>1</v>
@@ -1913,7 +1897,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="123" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6">
       <c r="A123" s="1" t="s">
         <v>2</v>
       </c>
@@ -1921,7 +1905,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6">
       <c r="A124" t="s">
         <v>4</v>
       </c>
@@ -1929,7 +1913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6">
       <c r="A125" t="s">
         <v>5</v>
       </c>
@@ -1937,7 +1921,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6">
       <c r="A126" t="s">
         <v>6</v>
       </c>
@@ -1945,7 +1929,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:6">
       <c r="A127" t="s">
         <v>7</v>
       </c>
@@ -1953,7 +1937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:6">
       <c r="A128" t="s">
         <v>8</v>
       </c>
@@ -1961,7 +1945,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6">
       <c r="A129" t="s">
         <v>10</v>
       </c>
@@ -1969,12 +1953,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="130" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:6">
       <c r="A130" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:6">
       <c r="A131" t="s">
         <v>13</v>
       </c>
@@ -1994,7 +1978,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:6">
       <c r="A132" t="s">
         <v>44</v>
       </c>
@@ -2011,12 +1995,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:6">
       <c r="A133" t="s">
         <v>3</v>
       </c>
       <c r="B133">
-        <v>0.84602368866328259</v>
+        <v>0.8460236886632826</v>
       </c>
       <c r="C133" t="s">
         <v>1</v>
@@ -2028,12 +2012,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:6">
       <c r="A134" t="s">
         <v>52</v>
       </c>
       <c r="B134">
-        <v>0.15397631133671741</v>
+        <v>0.1539763113367174</v>
       </c>
       <c r="C134" t="s">
         <v>1</v>
@@ -2045,7 +2029,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:6">
       <c r="A135" t="s">
         <v>22</v>
       </c>
@@ -2062,7 +2046,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="137" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:6">
       <c r="A137" s="1" t="s">
         <v>2</v>
       </c>
@@ -2070,7 +2054,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:6">
       <c r="A138" t="s">
         <v>4</v>
       </c>
@@ -2078,7 +2062,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:6">
       <c r="A139" t="s">
         <v>5</v>
       </c>
@@ -2086,7 +2070,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:6">
       <c r="A140" t="s">
         <v>6</v>
       </c>
@@ -2094,7 +2078,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:6">
       <c r="A141" t="s">
         <v>7</v>
       </c>
@@ -2102,7 +2086,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:6">
       <c r="A142" t="s">
         <v>8</v>
       </c>
@@ -2110,7 +2094,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:6">
       <c r="A143" t="s">
         <v>10</v>
       </c>
@@ -2118,12 +2102,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="144" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:6">
       <c r="A144" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:6">
       <c r="A145" t="s">
         <v>13</v>
       </c>
@@ -2143,12 +2127,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:6">
       <c r="A146" t="s">
         <v>53</v>
       </c>
       <c r="B146">
-        <v>1.6607142857142859E-4</v>
+        <v>0.0001660714285714286</v>
       </c>
       <c r="D146" t="s">
         <v>11</v>
@@ -2160,7 +2144,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6">
       <c r="A147" t="s">
         <v>27</v>
       </c>
@@ -2177,7 +2161,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:6">
       <c r="A148" t="s">
         <v>30</v>
       </c>
@@ -2194,7 +2178,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:6">
       <c r="A149" t="s">
         <v>32</v>
       </c>
@@ -2211,7 +2195,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:6">
       <c r="A150" t="s">
         <v>15</v>
       </c>
@@ -2228,7 +2212,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:6">
       <c r="A151" t="s">
         <v>36</v>
       </c>
@@ -2245,7 +2229,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:6">
       <c r="A152" t="s">
         <v>3</v>
       </c>
@@ -2262,7 +2246,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:6">
       <c r="A153" t="s">
         <v>54</v>
       </c>
@@ -2279,12 +2263,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:6">
       <c r="A154" t="s">
         <v>22</v>
       </c>
       <c r="B154">
-        <v>1.6565131578947359E-4</v>
+        <v>0.0001656513157894736</v>
       </c>
       <c r="C154" t="s">
         <v>23</v>
@@ -2296,7 +2280,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:6">
       <c r="A155" t="s">
         <v>56</v>
       </c>
@@ -2313,12 +2297,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:6">
       <c r="A156" t="s">
         <v>57</v>
       </c>
       <c r="B156">
-        <v>9.0000000000000006E-5</v>
+        <v>9.000000000000001E-05</v>
       </c>
       <c r="C156" t="s">
         <v>40</v>
@@ -2330,7 +2314,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:6">
       <c r="A157" t="s">
         <v>58</v>
       </c>
@@ -2347,12 +2331,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:6">
       <c r="A158" t="s">
         <v>34</v>
       </c>
       <c r="B158">
-        <v>-5.0000000000000002E-5</v>
+        <v>-5E-05</v>
       </c>
       <c r="C158" t="s">
         <v>1</v>
@@ -2364,7 +2348,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="160" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:6">
       <c r="A160" s="1" t="s">
         <v>2</v>
       </c>
@@ -2372,7 +2356,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:6">
       <c r="A161" t="s">
         <v>4</v>
       </c>
@@ -2380,7 +2364,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:6">
       <c r="A162" t="s">
         <v>5</v>
       </c>
@@ -2388,7 +2372,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:6">
       <c r="A163" t="s">
         <v>6</v>
       </c>
@@ -2396,7 +2380,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:6">
       <c r="A164" t="s">
         <v>7</v>
       </c>
@@ -2404,7 +2388,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:6">
       <c r="A165" t="s">
         <v>8</v>
       </c>
@@ -2412,7 +2396,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:6">
       <c r="A166" t="s">
         <v>10</v>
       </c>
@@ -2420,12 +2404,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="167" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:6">
       <c r="A167" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:6">
       <c r="A168" t="s">
         <v>13</v>
       </c>
@@ -2445,12 +2429,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:6">
       <c r="A169" t="s">
         <v>60</v>
       </c>
       <c r="B169">
-        <v>-2.3000000000000001E-4</v>
+        <v>-0.00023</v>
       </c>
       <c r="D169" t="s">
         <v>11</v>
@@ -2462,12 +2446,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:6">
       <c r="A170" t="s">
         <v>43</v>
       </c>
       <c r="B170">
-        <v>-1.6199999999999999E-3</v>
+        <v>-0.00162</v>
       </c>
       <c r="D170" t="s">
         <v>38</v>
@@ -2479,12 +2463,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:6">
       <c r="A171" t="s">
         <v>62</v>
       </c>
       <c r="B171">
-        <v>-7.0000000000000007E-5</v>
+        <v>-7.000000000000001E-05</v>
       </c>
       <c r="D171" t="s">
         <v>11</v>
@@ -2496,7 +2480,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:6">
       <c r="A172" t="s">
         <v>59</v>
       </c>
@@ -2513,12 +2497,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:6">
       <c r="A173" t="s">
         <v>3</v>
       </c>
       <c r="B173">
-        <v>0.13750000000000001</v>
+        <v>0.1375</v>
       </c>
       <c r="C173" t="s">
         <v>1</v>
@@ -2530,7 +2514,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:6">
       <c r="A174" t="s">
         <v>35</v>
       </c>
@@ -2547,12 +2531,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:6">
       <c r="A175" t="s">
         <v>22</v>
       </c>
       <c r="B175">
-        <v>8.1999999999999998E-4</v>
+        <v>0.00082</v>
       </c>
       <c r="C175" t="s">
         <v>23</v>
@@ -2564,12 +2548,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:6">
       <c r="A176" t="s">
         <v>63</v>
       </c>
       <c r="B176">
-        <v>2.4000000000000001E-4</v>
+        <v>0.00024</v>
       </c>
       <c r="C176" t="s">
         <v>40</v>
@@ -2581,12 +2565,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:6">
       <c r="A177" t="s">
         <v>64</v>
       </c>
       <c r="B177">
-        <v>1.2E-4</v>
+        <v>0.00012</v>
       </c>
       <c r="C177" t="s">
         <v>47</v>
@@ -2598,7 +2582,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="179" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:6">
       <c r="A179" s="1" t="s">
         <v>2</v>
       </c>
@@ -2606,7 +2590,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:6">
       <c r="A180" t="s">
         <v>4</v>
       </c>
@@ -2614,7 +2598,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:6">
       <c r="A181" t="s">
         <v>5</v>
       </c>
@@ -2622,7 +2606,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:6">
       <c r="A182" t="s">
         <v>6</v>
       </c>
@@ -2630,7 +2614,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:6">
       <c r="A183" t="s">
         <v>7</v>
       </c>
@@ -2638,7 +2622,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:6">
       <c r="A184" t="s">
         <v>8</v>
       </c>
@@ -2646,7 +2630,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:6">
       <c r="A185" t="s">
         <v>10</v>
       </c>
@@ -2654,12 +2638,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="186" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:6">
       <c r="A186" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:6">
       <c r="A187" t="s">
         <v>13</v>
       </c>
@@ -2679,7 +2663,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:6">
       <c r="A188" t="s">
         <v>65</v>
       </c>
@@ -2696,7 +2680,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:6">
       <c r="A189" t="s">
         <v>59</v>
       </c>
@@ -2713,7 +2697,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:6">
       <c r="A190" t="s">
         <v>22</v>
       </c>
@@ -2730,7 +2714,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="192" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:6">
       <c r="A192" s="1" t="s">
         <v>2</v>
       </c>
@@ -2738,7 +2722,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:6">
       <c r="A193" t="s">
         <v>4</v>
       </c>
@@ -2746,7 +2730,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:6">
       <c r="A194" t="s">
         <v>5</v>
       </c>
@@ -2754,7 +2738,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:6">
       <c r="A195" t="s">
         <v>6</v>
       </c>
@@ -2762,7 +2746,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:6">
       <c r="A196" t="s">
         <v>7</v>
       </c>
@@ -2770,7 +2754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:6">
       <c r="A197" t="s">
         <v>8</v>
       </c>
@@ -2778,7 +2762,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:6">
       <c r="A198" t="s">
         <v>10</v>
       </c>
@@ -2786,12 +2770,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="199" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:6">
       <c r="A199" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:6">
       <c r="A200" t="s">
         <v>13</v>
       </c>
@@ -2811,7 +2795,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:6">
       <c r="A201" t="s">
         <v>33</v>
       </c>
@@ -2828,7 +2812,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:6">
       <c r="A202" t="s">
         <v>65</v>
       </c>
@@ -2845,12 +2829,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:6">
       <c r="A203" t="s">
         <v>22</v>
       </c>
       <c r="B203">
-        <v>5.5659999999999998E-3</v>
+        <v>0.005566</v>
       </c>
       <c r="C203" t="s">
         <v>23</v>
@@ -2862,7 +2846,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="205" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:6">
       <c r="A205" s="1" t="s">
         <v>2</v>
       </c>
@@ -2870,7 +2854,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:6">
       <c r="A206" t="s">
         <v>4</v>
       </c>
@@ -2878,7 +2862,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:6">
       <c r="A207" t="s">
         <v>5</v>
       </c>
@@ -2886,7 +2870,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:6">
       <c r="A208" t="s">
         <v>6</v>
       </c>
@@ -2894,7 +2878,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:6">
       <c r="A209" t="s">
         <v>7</v>
       </c>
@@ -2902,7 +2886,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:6">
       <c r="A210" t="s">
         <v>8</v>
       </c>
@@ -2910,7 +2894,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:6">
       <c r="A211" t="s">
         <v>10</v>
       </c>
@@ -2918,12 +2902,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="212" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:6">
       <c r="A212" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:6">
       <c r="A213" t="s">
         <v>13</v>
       </c>
@@ -2943,7 +2927,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:6">
       <c r="A214" t="s">
         <v>43</v>
       </c>
@@ -2960,7 +2944,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:6">
       <c r="A215" t="s">
         <v>66</v>
       </c>
@@ -2977,7 +2961,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:6">
       <c r="A216" t="s">
         <v>50</v>
       </c>
@@ -2994,12 +2978,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:6">
       <c r="A217" t="s">
         <v>37</v>
       </c>
       <c r="B217">
-        <v>0.35294117647058831</v>
+        <v>0.3529411764705883</v>
       </c>
       <c r="C217" t="s">
         <v>1</v>
@@ -3011,7 +2995,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:6">
       <c r="A218" t="s">
         <v>22</v>
       </c>
@@ -3028,7 +3012,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="220" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:6">
       <c r="A220" s="1" t="s">
         <v>2</v>
       </c>
@@ -3036,7 +3020,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:6">
       <c r="A221" t="s">
         <v>4</v>
       </c>
@@ -3044,7 +3028,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:6">
       <c r="A222" t="s">
         <v>5</v>
       </c>
@@ -3052,7 +3036,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:6">
       <c r="A223" t="s">
         <v>6</v>
       </c>
@@ -3060,7 +3044,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:6">
       <c r="A224" t="s">
         <v>7</v>
       </c>
@@ -3068,7 +3052,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:6">
       <c r="A225" t="s">
         <v>8</v>
       </c>
@@ -3076,7 +3060,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:6">
       <c r="A226" t="s">
         <v>10</v>
       </c>
@@ -3084,12 +3068,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="227" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:6">
       <c r="A227" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:6">
       <c r="A228" t="s">
         <v>13</v>
       </c>
@@ -3109,7 +3093,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:6">
       <c r="A229" t="s">
         <v>51</v>
       </c>
@@ -3126,7 +3110,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:6">
       <c r="A230" t="s">
         <v>3</v>
       </c>
@@ -3143,12 +3127,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:6">
       <c r="A231" t="s">
         <v>48</v>
       </c>
       <c r="B231">
-        <v>0.42857142857142849</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="C231" t="s">
         <v>1</v>
@@ -3160,12 +3144,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:6">
       <c r="A232" t="s">
         <v>37</v>
       </c>
       <c r="B232">
-        <v>0.24360307899159661</v>
+        <v>0.2436030789915966</v>
       </c>
       <c r="C232" t="s">
         <v>1</v>
@@ -3177,7 +3161,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="234" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:6">
       <c r="A234" s="1" t="s">
         <v>2</v>
       </c>
@@ -3185,7 +3169,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:6">
       <c r="A235" t="s">
         <v>4</v>
       </c>
@@ -3193,7 +3177,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:6">
       <c r="A236" t="s">
         <v>5</v>
       </c>
@@ -3201,7 +3185,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:6">
       <c r="A237" t="s">
         <v>6</v>
       </c>
@@ -3209,7 +3193,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:6">
       <c r="A238" t="s">
         <v>7</v>
       </c>
@@ -3217,7 +3201,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:6">
       <c r="A239" t="s">
         <v>8</v>
       </c>
@@ -3225,7 +3209,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:6">
       <c r="A240" t="s">
         <v>10</v>
       </c>
@@ -3233,12 +3217,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="241" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:6">
       <c r="A241" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:6">
       <c r="A242" t="s">
         <v>13</v>
       </c>
@@ -3258,7 +3242,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:6">
       <c r="A243" t="s">
         <v>52</v>
       </c>
@@ -3275,7 +3259,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:6">
       <c r="A244" t="s">
         <v>3</v>
       </c>
@@ -3292,12 +3276,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:6">
       <c r="A245" t="s">
         <v>49</v>
       </c>
       <c r="B245">
-        <v>0.42857142857142849</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="C245" t="s">
         <v>1</v>
@@ -3309,12 +3293,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:6">
       <c r="A246" t="s">
         <v>37</v>
       </c>
       <c r="B246">
-        <v>0.24360307899159661</v>
+        <v>0.2436030789915966</v>
       </c>
       <c r="C246" t="s">
         <v>1</v>
@@ -3326,7 +3310,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="248" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:6">
       <c r="A248" s="1" t="s">
         <v>2</v>
       </c>
@@ -3334,7 +3318,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:6">
       <c r="A249" t="s">
         <v>4</v>
       </c>
@@ -3342,7 +3326,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:6">
       <c r="A250" t="s">
         <v>5</v>
       </c>
@@ -3350,7 +3334,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:6">
       <c r="A251" t="s">
         <v>6</v>
       </c>
@@ -3358,7 +3342,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:6">
       <c r="A252" t="s">
         <v>7</v>
       </c>
@@ -3366,7 +3350,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:6">
       <c r="A253" t="s">
         <v>8</v>
       </c>
@@ -3374,7 +3358,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:6">
       <c r="A254" t="s">
         <v>10</v>
       </c>
@@ -3382,12 +3366,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="255" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:6">
       <c r="A255" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:6">
       <c r="A256" t="s">
         <v>13</v>
       </c>
@@ -3407,7 +3391,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:6">
       <c r="A257" t="s">
         <v>15</v>
       </c>
@@ -3424,7 +3408,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:6">
       <c r="A258" t="s">
         <v>34</v>
       </c>
@@ -3441,7 +3425,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:6">
       <c r="A259" t="s">
         <v>67</v>
       </c>
